--- a/Input_minna_gagnasett.xlsx
+++ b/Input_minna_gagnasett.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FF0C21A-9826-4E1C-9315-041A4744057E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F488DF-4706-4CA4-9F5D-8D42203606C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
     <sheet name="Employees" sheetId="2" r:id="rId2"/>
     <sheet name="DaysOff" sheetId="4" r:id="rId3"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId4"/>
-    <sheet name="Score" sheetId="6" r:id="rId5"/>
+    <sheet name="ScoreKeys" sheetId="7" r:id="rId4"/>
+    <sheet name="SkillsetScores" sheetId="8" r:id="rId5"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId6"/>
+    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="124">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -382,6 +384,36 @@
   </si>
   <si>
     <t>Basic</t>
+  </si>
+  <si>
+    <t>Weekend</t>
+  </si>
+  <si>
+    <t>RuleType</t>
+  </si>
+  <si>
+    <t>Weekend_last_period</t>
+  </si>
+  <si>
+    <t>Shifts_this_week</t>
+  </si>
+  <si>
+    <t>Shifs_this_length</t>
+  </si>
+  <si>
+    <t>Shift_over_six_hours</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>ReqSkillset</t>
+  </si>
+  <si>
+    <t>EmpSkillset</t>
   </si>
 </sst>
 </file>
@@ -1218,6 +1250,455 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE134D07-2ED5-4277-9A21-369947BF3DF7}">
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <f>+C24*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <f>+C25*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <f>+C26*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>-50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EC1D4D2-5C1A-491D-B433-41D3ADCB02A2}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>-200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1603,23 +2084,33 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -1629,40 +2120,96 @@
       <c r="C2">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>65</v>
       </c>
       <c r="C5">
         <v>-10</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>66</v>
       </c>
       <c r="C6">
         <v>-50</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -1672,40 +2219,96 @@
       <c r="C8">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>70</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>71</v>
       </c>
       <c r="C11">
         <v>-25</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>72</v>
       </c>
       <c r="C12">
         <v>-50</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E12" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -1715,40 +2318,96 @@
       <c r="C14">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>75</v>
       </c>
       <c r="C15">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>76</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>77</v>
       </c>
       <c r="C17">
         <v>-10</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>78</v>
       </c>
       <c r="C18">
         <v>-20</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -1758,8 +2417,17 @@
       <c r="C20">
         <v>-10</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>81</v>
       </c>
@@ -1767,8 +2435,17 @@
         <f>+C20*2</f>
         <v>-20</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>82</v>
       </c>
@@ -1776,8 +2453,17 @@
         <f>+C21*2</f>
         <v>-40</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>83</v>
       </c>
@@ -1785,8 +2471,17 @@
         <f>+C22*2</f>
         <v>-80</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>84</v>
       </c>
@@ -1794,8 +2489,29 @@
         <f>+C23*2</f>
         <v>-160</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E24" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <f>+G24*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -1805,8 +2521,18 @@
       <c r="C26">
         <v>-1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E26" t="s">
+        <v>118</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <f>+G25*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>87</v>
       </c>
@@ -1814,8 +2540,18 @@
         <f>+C26*2</f>
         <v>-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E27" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27">
+        <f>+G26*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>88</v>
       </c>
@@ -1823,8 +2559,17 @@
         <f>+C27*2</f>
         <v>-4</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E28" t="s">
+        <v>119</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>89</v>
       </c>
@@ -1833,7 +2578,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>90</v>
       </c>

--- a/Input_minna_gagnasett.xlsx
+++ b/Input_minna_gagnasett.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F488DF-4706-4CA4-9F5D-8D42203606C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE2AB78-BAB2-4E36-B6D4-498D75DF62E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="125">
   <si>
     <t xml:space="preserve">1.5.2024 </t>
   </si>
@@ -326,9 +326,6 @@
     <t>Skillset</t>
   </si>
   <si>
-    <t>Ef þarf skillset 3 en þú ert ekki</t>
-  </si>
-  <si>
     <t>Ef þarf skillset 2 en þú ert 1</t>
   </si>
   <si>
@@ -344,9 +341,6 @@
     <t>Ef þarf skillset 1 og þú ert</t>
   </si>
   <si>
-    <t>Ef þarf skillset 1 og þú ert 2 eða 3</t>
-  </si>
-  <si>
     <t>Upprás</t>
   </si>
   <si>
@@ -414,6 +408,15 @@
   </si>
   <si>
     <t>EmpSkillset</t>
+  </si>
+  <si>
+    <t>bæta við category type?</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 1 en þú ert ekki</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
   </si>
 </sst>
 </file>
@@ -423,7 +426,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,6 +444,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -466,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -474,6 +484,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -832,7 +843,7 @@
         <v>52</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>59</v>
@@ -864,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
@@ -982,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K4" s="1">
         <v>0.75</v>
@@ -1025,7 +1036,7 @@
         <v>2</v>
       </c>
       <c r="J5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K5" s="1">
         <v>0.75</v>
@@ -1064,10 +1075,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>93</v>
@@ -1078,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1089,7 +1100,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1100,7 +1111,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1121,7 +1132,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1251,26 +1262,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE134D07-2ED5-4277-9A21-369947BF3DF7}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1279,9 +1290,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1290,9 +1301,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -1301,9 +1312,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -1312,9 +1323,9 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -1323,9 +1334,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1333,10 +1344,13 @@
       <c r="C7">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E7" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1345,9 +1359,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -1356,9 +1370,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -1367,9 +1381,9 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -1378,9 +1392,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -1389,7 +1403,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1400,7 +1414,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1411,7 +1425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1422,7 +1436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1457,7 +1471,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1468,7 +1482,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -1479,7 +1493,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B21">
         <v>3</v>
@@ -1490,7 +1504,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -1501,7 +1515,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -1512,7 +1526,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1523,7 +1537,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -1535,7 +1549,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -1547,7 +1561,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B27">
         <v>4</v>
@@ -1559,7 +1573,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -1585,21 +1599,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>3</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
       </c>
       <c r="C2">
         <v>-1000</v>
@@ -1607,7 +1621,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1621,7 +1635,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>-200</v>
@@ -1632,7 +1646,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>-50</v>
@@ -1640,10 +1654,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1662,10 +1676,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1673,7 +1687,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -1684,10 +1698,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>-200</v>
@@ -1716,7 +1730,7 @@
         <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>32</v>
@@ -1739,7 +1753,7 @@
         <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -1762,7 +1776,7 @@
         <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
@@ -1785,7 +1799,7 @@
         <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
@@ -1808,7 +1822,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
@@ -1831,7 +1845,7 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
@@ -1854,7 +1868,7 @@
         <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
@@ -1877,7 +1891,7 @@
         <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
         <v>36</v>
@@ -1900,7 +1914,7 @@
         <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -1923,7 +1937,7 @@
         <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -1969,7 +1983,7 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
@@ -1992,7 +2006,7 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
@@ -2015,7 +2029,7 @@
         <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
         <v>37</v>
@@ -2038,7 +2052,7 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>37</v>
@@ -2061,7 +2075,7 @@
         <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
         <v>51</v>
@@ -2101,13 +2115,13 @@
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="E1" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -2121,7 +2135,7 @@
         <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2138,7 +2152,7 @@
         <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2155,7 +2169,7 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -2172,7 +2186,7 @@
         <v>-10</v>
       </c>
       <c r="E5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -2189,7 +2203,7 @@
         <v>-50</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -2200,7 +2214,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2220,7 +2234,7 @@
         <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -2237,7 +2251,7 @@
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -2254,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -2271,7 +2285,7 @@
         <v>-25</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F11">
         <v>4</v>
@@ -2288,7 +2302,7 @@
         <v>-50</v>
       </c>
       <c r="E12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2398,7 +2412,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -2418,7 +2432,7 @@
         <v>-10</v>
       </c>
       <c r="E20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F20">
         <v>2</v>
@@ -2436,7 +2450,7 @@
         <v>-20</v>
       </c>
       <c r="E21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F21">
         <v>3</v>
@@ -2454,7 +2468,7 @@
         <v>-40</v>
       </c>
       <c r="E22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F22">
         <v>4</v>
@@ -2472,7 +2486,7 @@
         <v>-80</v>
       </c>
       <c r="E23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -2490,7 +2504,7 @@
         <v>-160</v>
       </c>
       <c r="E24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2501,7 +2515,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -2522,7 +2536,7 @@
         <v>-1</v>
       </c>
       <c r="E26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F26">
         <v>3</v>
@@ -2541,7 +2555,7 @@
         <v>-2</v>
       </c>
       <c r="E27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F27">
         <v>4</v>
@@ -2560,7 +2574,7 @@
         <v>-4</v>
       </c>
       <c r="E28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2599,7 +2613,7 @@
         <v>93</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="C35">
         <v>-1000</v>
@@ -2615,7 +2629,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C37">
         <v>-50</v>
@@ -2623,7 +2637,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C38">
         <v>1000</v>
@@ -2631,7 +2645,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -2639,7 +2653,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -2647,7 +2661,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C41">
         <v>-200</v>

--- a/Input_minna_gagnasett.xlsx
+++ b/Input_minna_gagnasett.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133114C8-FABA-4496-92DA-746A48FE238D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AEE56F-5BFB-469D-BAEE-C7F37B35AF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="2" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -486,10 +486,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -954,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" s="1">
         <v>0.66666666666666663</v>
@@ -1282,13 +1282,13 @@
       <c r="B1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>103</v>
       </c>
       <c r="F1" s="3"/>
@@ -2292,11 +2292,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
       <c r="E1" s="2" t="s">
         <v>113</v>
       </c>

--- a/Input_minna_gagnasett.xlsx
+++ b/Input_minna_gagnasett.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AEE56F-5BFB-469D-BAEE-C7F37B35AF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59079E6-F9CA-492E-AACB-FC3624655DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="2" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -954,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K3" s="1">
         <v>0.66666666666666663</v>
